--- a/artfynd/A 32314-2023 artfynd.xlsx
+++ b/artfynd/A 32314-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115045469</v>
+        <v>100743118</v>
       </c>
       <c r="B2" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarvarmossen, Srm</t>
+          <t>Svarvaretorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595374</v>
+        <v>595295</v>
       </c>
       <c r="R2" t="n">
-        <v>6579682</v>
+        <v>6579675</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I kanten på nyupptageg hygge</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,15 +764,121 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering (NVI) inför utbyggnad av regionnätet i Eskilstuna kommun </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115045469</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92348</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svarvarmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>595374</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6579682</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kjula</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I kanten på nyupptageg hygge</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Fredrik Enoksson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Fredrik Enoksson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32314-2023 artfynd.xlsx
+++ b/artfynd/A 32314-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t xml:space="preserve">Naturvärdesinventering (NVI) inför utbyggnad av regionnätet i Eskilstuna kommun </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100743118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>